--- a/artfynd/A 51330-2022 artfynd.xlsx
+++ b/artfynd/A 51330-2022 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067314</v>
+        <v>125067295</v>
       </c>
       <c r="B3" t="n">
-        <v>56725</v>
+        <v>56714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -818,18 +818,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534384</v>
+        <v>534253</v>
       </c>
       <c r="R3" t="n">
-        <v>6886731</v>
+        <v>6886812</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -899,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125067260</v>
+        <v>125067314</v>
       </c>
       <c r="B4" t="n">
         <v>56725</v>
@@ -932,14 +928,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534103</v>
+        <v>534384</v>
       </c>
       <c r="R4" t="n">
-        <v>6886914</v>
+        <v>6886731</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125067242</v>
+        <v>125067260</v>
       </c>
       <c r="B5" t="n">
         <v>56725</v>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534037</v>
+        <v>534103</v>
       </c>
       <c r="R5" t="n">
-        <v>6886910</v>
+        <v>6886914</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125067295</v>
+        <v>125067242</v>
       </c>
       <c r="B6" t="n">
-        <v>56714</v>
+        <v>56725</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,20 +1131,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534253</v>
+        <v>534037</v>
       </c>
       <c r="R6" t="n">
-        <v>6886812</v>
+        <v>6886910</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 51330-2022 artfynd.xlsx
+++ b/artfynd/A 51330-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125067275</v>
+        <v>125067242</v>
       </c>
       <c r="B2" t="n">
         <v>56725</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534161</v>
+        <v>534037</v>
       </c>
       <c r="R2" t="n">
-        <v>6886790</v>
+        <v>6886910</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067295</v>
+        <v>125067260</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>56725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534253</v>
+        <v>534103</v>
       </c>
       <c r="R3" t="n">
-        <v>6886812</v>
+        <v>6886914</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125067260</v>
+        <v>125067275</v>
       </c>
       <c r="B5" t="n">
         <v>56725</v>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534103</v>
+        <v>534161</v>
       </c>
       <c r="R5" t="n">
-        <v>6886914</v>
+        <v>6886790</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125067242</v>
+        <v>125067295</v>
       </c>
       <c r="B6" t="n">
-        <v>56725</v>
+        <v>56714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,20 +1131,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534037</v>
+        <v>534253</v>
       </c>
       <c r="R6" t="n">
-        <v>6886910</v>
+        <v>6886812</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 51330-2022 artfynd.xlsx
+++ b/artfynd/A 51330-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125067242</v>
+        <v>125067314</v>
       </c>
       <c r="B2" t="n">
         <v>56725</v>
@@ -708,14 +708,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534037</v>
+        <v>534384</v>
       </c>
       <c r="R2" t="n">
-        <v>6886910</v>
+        <v>6886731</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -785,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067260</v>
+        <v>125067295</v>
       </c>
       <c r="B3" t="n">
-        <v>56725</v>
+        <v>56714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,20 +801,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534103</v>
+        <v>534253</v>
       </c>
       <c r="R3" t="n">
-        <v>6886914</v>
+        <v>6886812</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -895,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125067314</v>
+        <v>125067242</v>
       </c>
       <c r="B4" t="n">
         <v>56725</v>
@@ -928,18 +932,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534384</v>
+        <v>534037</v>
       </c>
       <c r="R4" t="n">
-        <v>6886731</v>
+        <v>6886910</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125067275</v>
+        <v>125067260</v>
       </c>
       <c r="B5" t="n">
         <v>56725</v>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534161</v>
+        <v>534103</v>
       </c>
       <c r="R5" t="n">
-        <v>6886790</v>
+        <v>6886914</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125067295</v>
+        <v>125067275</v>
       </c>
       <c r="B6" t="n">
-        <v>56714</v>
+        <v>56725</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,20 +1131,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534253</v>
+        <v>534161</v>
       </c>
       <c r="R6" t="n">
-        <v>6886812</v>
+        <v>6886790</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 51330-2022 artfynd.xlsx
+++ b/artfynd/A 51330-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125067314</v>
+        <v>125067242</v>
       </c>
       <c r="B2" t="n">
         <v>56725</v>
@@ -708,18 +708,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534384</v>
+        <v>534037</v>
       </c>
       <c r="R2" t="n">
-        <v>6886731</v>
+        <v>6886910</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067295</v>
+        <v>125067275</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>56725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,20 +797,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534253</v>
+        <v>534161</v>
       </c>
       <c r="R3" t="n">
-        <v>6886812</v>
+        <v>6886790</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -899,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125067242</v>
+        <v>125067314</v>
       </c>
       <c r="B4" t="n">
         <v>56725</v>
@@ -932,14 +928,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534037</v>
+        <v>534384</v>
       </c>
       <c r="R4" t="n">
-        <v>6886910</v>
+        <v>6886731</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125067275</v>
+        <v>125067295</v>
       </c>
       <c r="B6" t="n">
-        <v>56725</v>
+        <v>56714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,20 +1131,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534161</v>
+        <v>534253</v>
       </c>
       <c r="R6" t="n">
-        <v>6886790</v>
+        <v>6886812</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 51330-2022 artfynd.xlsx
+++ b/artfynd/A 51330-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125067242</v>
+        <v>125067275</v>
       </c>
       <c r="B2" t="n">
         <v>56725</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534037</v>
+        <v>534161</v>
       </c>
       <c r="R2" t="n">
-        <v>6886910</v>
+        <v>6886790</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067275</v>
+        <v>125067260</v>
       </c>
       <c r="B3" t="n">
         <v>56725</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534161</v>
+        <v>534103</v>
       </c>
       <c r="R3" t="n">
-        <v>6886790</v>
+        <v>6886914</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125067260</v>
+        <v>125067242</v>
       </c>
       <c r="B5" t="n">
         <v>56725</v>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534103</v>
+        <v>534037</v>
       </c>
       <c r="R5" t="n">
-        <v>6886914</v>
+        <v>6886910</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>

--- a/artfynd/A 51330-2022 artfynd.xlsx
+++ b/artfynd/A 51330-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125067275</v>
+        <v>125067260</v>
       </c>
       <c r="B2" t="n">
         <v>56725</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534161</v>
+        <v>534103</v>
       </c>
       <c r="R2" t="n">
-        <v>6886790</v>
+        <v>6886914</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067260</v>
+        <v>125067242</v>
       </c>
       <c r="B3" t="n">
         <v>56725</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534103</v>
+        <v>534037</v>
       </c>
       <c r="R3" t="n">
-        <v>6886914</v>
+        <v>6886910</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125067314</v>
+        <v>125067275</v>
       </c>
       <c r="B4" t="n">
         <v>56725</v>
@@ -928,18 +928,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534384</v>
+        <v>534161</v>
       </c>
       <c r="R4" t="n">
-        <v>6886731</v>
+        <v>6886790</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1009,7 +1005,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125067242</v>
+        <v>125067314</v>
       </c>
       <c r="B5" t="n">
         <v>56725</v>
@@ -1042,14 +1038,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534037</v>
+        <v>534384</v>
       </c>
       <c r="R5" t="n">
-        <v>6886910</v>
+        <v>6886731</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>

--- a/artfynd/A 51330-2022 artfynd.xlsx
+++ b/artfynd/A 51330-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125067260</v>
+        <v>125067275</v>
       </c>
       <c r="B2" t="n">
         <v>56725</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534103</v>
+        <v>534161</v>
       </c>
       <c r="R2" t="n">
-        <v>6886914</v>
+        <v>6886790</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067242</v>
+        <v>125067260</v>
       </c>
       <c r="B3" t="n">
         <v>56725</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534037</v>
+        <v>534103</v>
       </c>
       <c r="R3" t="n">
-        <v>6886910</v>
+        <v>6886914</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125067275</v>
+        <v>125067295</v>
       </c>
       <c r="B4" t="n">
-        <v>56725</v>
+        <v>56714</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,20 +907,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534161</v>
+        <v>534253</v>
       </c>
       <c r="R4" t="n">
-        <v>6886790</v>
+        <v>6886812</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125067295</v>
+        <v>125067242</v>
       </c>
       <c r="B6" t="n">
-        <v>56714</v>
+        <v>56725</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,20 +1131,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534253</v>
+        <v>534037</v>
       </c>
       <c r="R6" t="n">
-        <v>6886812</v>
+        <v>6886910</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 51330-2022 artfynd.xlsx
+++ b/artfynd/A 51330-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125067275</v>
+        <v>125067295</v>
       </c>
       <c r="B2" t="n">
-        <v>56725</v>
+        <v>56714</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534161</v>
+        <v>534253</v>
       </c>
       <c r="R2" t="n">
-        <v>6886790</v>
+        <v>6886812</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -778,14 +778,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ellen Payne, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Ellen Payne</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067260</v>
+        <v>125067242</v>
       </c>
       <c r="B3" t="n">
         <v>56725</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534103</v>
+        <v>534037</v>
       </c>
       <c r="R3" t="n">
-        <v>6886914</v>
+        <v>6886910</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125067295</v>
+        <v>125067260</v>
       </c>
       <c r="B4" t="n">
-        <v>56714</v>
+        <v>56725</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,20 +907,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534253</v>
+        <v>534103</v>
       </c>
       <c r="R4" t="n">
-        <v>6886812</v>
+        <v>6886914</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,14 +998,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ellen Payne, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Ellen Payne</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125067314</v>
+        <v>125067275</v>
       </c>
       <c r="B5" t="n">
         <v>56725</v>
@@ -1038,18 +1038,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1057,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534384</v>
+        <v>534161</v>
       </c>
       <c r="R5" t="n">
-        <v>6886731</v>
+        <v>6886790</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1112,14 +1108,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ellen Payne, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Ellen Payne</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125067242</v>
+        <v>125067314</v>
       </c>
       <c r="B6" t="n">
         <v>56725</v>
@@ -1152,14 +1148,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534037</v>
+        <v>534384</v>
       </c>
       <c r="R6" t="n">
-        <v>6886910</v>
+        <v>6886731</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 51330-2022 artfynd.xlsx
+++ b/artfynd/A 51330-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125067295</v>
       </c>
       <c r="B2" t="n">
-        <v>56714</v>
+        <v>56828</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -778,17 +778,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Ellen Payne</t>
+          <t>Ellen Payne, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067242</v>
+        <v>125067275</v>
       </c>
       <c r="B3" t="n">
-        <v>56725</v>
+        <v>56839</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534037</v>
+        <v>534161</v>
       </c>
       <c r="R3" t="n">
-        <v>6886910</v>
+        <v>6886790</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125067260</v>
+        <v>125067314</v>
       </c>
       <c r="B4" t="n">
-        <v>56725</v>
+        <v>56839</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,14 +928,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534103</v>
+        <v>534384</v>
       </c>
       <c r="R4" t="n">
-        <v>6886914</v>
+        <v>6886731</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,17 +1002,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Ellen Payne</t>
+          <t>Ellen Payne, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125067275</v>
+        <v>125067242</v>
       </c>
       <c r="B5" t="n">
-        <v>56725</v>
+        <v>56839</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534161</v>
+        <v>534037</v>
       </c>
       <c r="R5" t="n">
-        <v>6886790</v>
+        <v>6886910</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1108,17 +1112,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Ellen Payne</t>
+          <t>Ellen Payne, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125067314</v>
+        <v>125067260</v>
       </c>
       <c r="B6" t="n">
-        <v>56725</v>
+        <v>56839</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,18 +1152,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534384</v>
+        <v>534103</v>
       </c>
       <c r="R6" t="n">
-        <v>6886731</v>
+        <v>6886914</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 51330-2022 artfynd.xlsx
+++ b/artfynd/A 51330-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125067295</v>
+        <v>125067314</v>
       </c>
       <c r="B2" t="n">
-        <v>56828</v>
+        <v>56839</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,14 +708,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534253</v>
+        <v>534384</v>
       </c>
       <c r="R2" t="n">
-        <v>6886812</v>
+        <v>6886731</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -785,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067275</v>
+        <v>125067242</v>
       </c>
       <c r="B3" t="n">
         <v>56839</v>
@@ -833,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534161</v>
+        <v>534037</v>
       </c>
       <c r="R3" t="n">
-        <v>6886790</v>
+        <v>6886910</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -895,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125067314</v>
+        <v>125067260</v>
       </c>
       <c r="B4" t="n">
         <v>56839</v>
@@ -928,18 +932,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534384</v>
+        <v>534103</v>
       </c>
       <c r="R4" t="n">
-        <v>6886731</v>
+        <v>6886914</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125067242</v>
+        <v>125067295</v>
       </c>
       <c r="B5" t="n">
-        <v>56839</v>
+        <v>56828</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,20 +1021,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534037</v>
+        <v>534253</v>
       </c>
       <c r="R5" t="n">
-        <v>6886910</v>
+        <v>6886812</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125067260</v>
+        <v>125067275</v>
       </c>
       <c r="B6" t="n">
         <v>56839</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534103</v>
+        <v>534161</v>
       </c>
       <c r="R6" t="n">
-        <v>6886914</v>
+        <v>6886790</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 51330-2022 artfynd.xlsx
+++ b/artfynd/A 51330-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125067242</v>
+        <v>125067295</v>
       </c>
       <c r="B2" t="n">
-        <v>56846</v>
+        <v>57132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534037</v>
+        <v>534253</v>
       </c>
       <c r="R2" t="n">
-        <v>6886910</v>
+        <v>6886812</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -780,27 +780,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125067295</v>
+        <v>125067242</v>
       </c>
       <c r="B3" t="n">
-        <v>56834</v>
+        <v>57144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534253</v>
+        <v>534037</v>
       </c>
       <c r="R3" t="n">
-        <v>6886812</v>
+        <v>6886910</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125067314</v>
+        <v>125067260</v>
       </c>
       <c r="B4" t="n">
-        <v>56846</v>
+        <v>57144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,18 +913,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534384</v>
+        <v>534103</v>
       </c>
       <c r="R4" t="n">
-        <v>6886731</v>
+        <v>6886914</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -997,7 +993,7 @@
         <v>125067275</v>
       </c>
       <c r="B5" t="n">
-        <v>56846</v>
+        <v>57144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125067260</v>
+        <v>125067314</v>
       </c>
       <c r="B6" t="n">
-        <v>56846</v>
+        <v>57144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,14 +1123,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534103</v>
+        <v>534384</v>
       </c>
       <c r="R6" t="n">
-        <v>6886914</v>
+        <v>6886731</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 51330-2022 artfynd.xlsx
+++ b/artfynd/A 51330-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125067295</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125067242</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125067260</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125067275</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,8 +1226,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125067314</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>